--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>135843493</v>
       </c>
       <c r="B5" t="n">
-        <v>92241</v>
+        <v>92243</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135843492</v>
       </c>
       <c r="B6" t="n">
-        <v>92262</v>
+        <v>92264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135840219</v>
       </c>
       <c r="B7" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135840223</v>
       </c>
       <c r="B8" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135843487</v>
       </c>
       <c r="B9" t="n">
-        <v>92713</v>
+        <v>92715</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ18"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,48 +1912,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135843491</v>
+        <v>136007930</v>
       </c>
       <c r="B13" t="n">
-        <v>57980</v>
+        <v>80561</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergsmannijärvi, T lm</t>
+          <t>bergmannivaara, T lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>752361</v>
+        <v>752264</v>
       </c>
       <c r="R13" t="n">
-        <v>7519839</v>
+        <v>7519899</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1977,27 +1977,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,27 +2007,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135843491</t>
+          <t>https://artportalen.se/Sighting/136007930</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135843489</v>
+        <v>135843491</v>
       </c>
       <c r="B14" t="n">
-        <v>58143</v>
+        <v>57980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103022</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,13 +2059,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>752370</v>
+        <v>752361</v>
       </c>
       <c r="R14" t="n">
-        <v>7519864</v>
+        <v>7519839</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2099,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2104,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,16 +2135,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135843489</t>
+          <t>https://artportalen.se/Sighting/135843491</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135834021</v>
+        <v>135843489</v>
       </c>
       <c r="B15" t="n">
-        <v>58084</v>
+        <v>58143</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2152,41 +2152,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>103022</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Boddaert, 1783)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bergsmannivaara, Bergsmannivaara, T lm</t>
+          <t>Bergsmannijärvi, T lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>752226</v>
+        <v>752370</v>
       </c>
       <c r="R15" t="n">
-        <v>7519924</v>
+        <v>7519864</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2215,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2225,7 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2240,27 +2236,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Anna Öhlund, Christina Boyd, per-erik mukka</t>
+          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135834021</t>
+          <t>https://artportalen.se/Sighting/135843489</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135840222</v>
+        <v>135834021</v>
       </c>
       <c r="B16" t="n">
-        <v>79464</v>
+        <v>58084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2268,37 +2264,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>260591</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bergsmannivaara, T lm</t>
+          <t>Bergsmannivaara, Bergsmannivaara, T lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>752348</v>
+        <v>752226</v>
       </c>
       <c r="R16" t="n">
-        <v>7519890</v>
+        <v>7519924</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2352,65 +2352,65 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Stefan Andersson, Anna Öhlund, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840222</t>
+          <t>https://artportalen.se/Sighting/135834021</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135840227</v>
+        <v>136007931</v>
       </c>
       <c r="B17" t="n">
-        <v>79464</v>
+        <v>98144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>260591</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bergsmannivaara, T lm</t>
+          <t>bergmannivaara, T lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>752367</v>
+        <v>752255</v>
       </c>
       <c r="R17" t="n">
-        <v>7519787</v>
+        <v>7519894</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2434,22 +2434,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2458,7 +2458,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2470,19 +2469,19 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840227</t>
+          <t>https://artportalen.se/Sighting/136007931</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135840228</v>
+        <v>135840222</v>
       </c>
       <c r="B18" t="n">
         <v>79464</v>
@@ -2517,10 +2516,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>752378</v>
+        <v>752348</v>
       </c>
       <c r="R18" t="n">
-        <v>7519790</v>
+        <v>7519890</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2552,7 +2551,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,7 +2561,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2587,6 +2586,231 @@
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135840222</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135840227</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bergsmannivaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>752367</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7519787</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135840227</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135840228</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bergsmannivaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>752378</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7519790</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135840228</t>
         </is>
@@ -2611,6 +2835,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135840233</v>
       </c>
       <c r="B2" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,7 +795,7 @@
         <v>135840235</v>
       </c>
       <c r="B3" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -907,7 +907,7 @@
         <v>135840236</v>
       </c>
       <c r="B4" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1019,7 +1019,7 @@
         <v>135843493</v>
       </c>
       <c r="B5" t="n">
-        <v>92243</v>
+        <v>92257</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135843492</v>
       </c>
       <c r="B6" t="n">
-        <v>92264</v>
+        <v>92278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135840219</v>
       </c>
       <c r="B7" t="n">
-        <v>91972</v>
+        <v>91986</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1355,7 +1355,7 @@
         <v>135840223</v>
       </c>
       <c r="B8" t="n">
-        <v>91972</v>
+        <v>91986</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1467,7 +1467,7 @@
         <v>135843487</v>
       </c>
       <c r="B9" t="n">
-        <v>92715</v>
+        <v>92730</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135840232</v>
       </c>
       <c r="B10" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1691,7 +1691,7 @@
         <v>135840211</v>
       </c>
       <c r="B11" t="n">
-        <v>80450</v>
+        <v>80452</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+          <t>Christina Boyd, Stefan Andersson, per-erik mukka, Anna Öhlund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1803,7 +1803,7 @@
         <v>135840213</v>
       </c>
       <c r="B12" t="n">
-        <v>80450</v>
+        <v>80452</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+          <t>Christina Boyd, Stefan Andersson, per-erik mukka, Anna Öhlund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1915,7 +1915,7 @@
         <v>136007930</v>
       </c>
       <c r="B13" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135843491</v>
       </c>
       <c r="B14" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>135843489</v>
       </c>
       <c r="B15" t="n">
-        <v>58143</v>
+        <v>58145</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>135834021</v>
       </c>
       <c r="B16" t="n">
-        <v>58084</v>
+        <v>58086</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>136007931</v>
       </c>
       <c r="B17" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>135840222</v>
       </c>
       <c r="B18" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2596,7 +2596,7 @@
         <v>135840227</v>
       </c>
       <c r="B19" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2709,7 +2709,7 @@
         <v>135840228</v>
       </c>
       <c r="B20" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -892,7 +892,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Christina Boyd, Stefan Andersson, per-erik mukka, Anna Öhlund</t>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Christina Boyd, Stefan Andersson, per-erik mukka, Anna Öhlund</t>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135840233</v>
       </c>
       <c r="B2" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135840235</v>
       </c>
       <c r="B3" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135840236</v>
       </c>
       <c r="B4" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135843493</v>
       </c>
       <c r="B5" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135843492</v>
       </c>
       <c r="B6" t="n">
-        <v>92278</v>
+        <v>92279</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135840219</v>
       </c>
       <c r="B7" t="n">
-        <v>91986</v>
+        <v>91987</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135840223</v>
       </c>
       <c r="B8" t="n">
-        <v>91986</v>
+        <v>91987</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135843487</v>
       </c>
       <c r="B9" t="n">
-        <v>92730</v>
+        <v>92731</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135840232</v>
       </c>
       <c r="B10" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135840211</v>
       </c>
       <c r="B11" t="n">
-        <v>80452</v>
+        <v>80453</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135840213</v>
       </c>
       <c r="B12" t="n">
-        <v>80452</v>
+        <v>80453</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136007930</v>
       </c>
       <c r="B13" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>136007931</v>
       </c>
       <c r="B17" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>135840222</v>
       </c>
       <c r="B18" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>135840227</v>
       </c>
       <c r="B19" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>135840228</v>
       </c>
       <c r="B20" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>135843493</v>
       </c>
       <c r="B5" t="n">
-        <v>92258</v>
+        <v>92259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135843492</v>
       </c>
       <c r="B6" t="n">
-        <v>92279</v>
+        <v>92280</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135840219</v>
       </c>
       <c r="B7" t="n">
-        <v>91987</v>
+        <v>91988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135840223</v>
       </c>
       <c r="B8" t="n">
-        <v>91987</v>
+        <v>91988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135843487</v>
       </c>
       <c r="B9" t="n">
-        <v>92731</v>
+        <v>92732</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>136007931</v>
       </c>
       <c r="B17" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135840233</v>
       </c>
       <c r="B2" t="n">
-        <v>79523</v>
+        <v>79524</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135840235</v>
       </c>
       <c r="B3" t="n">
-        <v>79523</v>
+        <v>79524</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135840236</v>
       </c>
       <c r="B4" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135843493</v>
       </c>
       <c r="B5" t="n">
-        <v>92259</v>
+        <v>92260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135843492</v>
       </c>
       <c r="B6" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135840219</v>
       </c>
       <c r="B7" t="n">
-        <v>91988</v>
+        <v>91989</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135840223</v>
       </c>
       <c r="B8" t="n">
-        <v>91988</v>
+        <v>91989</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135843487</v>
       </c>
       <c r="B9" t="n">
-        <v>92732</v>
+        <v>92733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135840232</v>
       </c>
       <c r="B10" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135840211</v>
       </c>
       <c r="B11" t="n">
-        <v>80453</v>
+        <v>80454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135840213</v>
       </c>
       <c r="B12" t="n">
-        <v>80453</v>
+        <v>80454</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136007930</v>
       </c>
       <c r="B13" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135843491</v>
       </c>
       <c r="B14" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>135843489</v>
       </c>
       <c r="B15" t="n">
-        <v>58145</v>
+        <v>58146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>135834021</v>
       </c>
       <c r="B16" t="n">
-        <v>58086</v>
+        <v>58087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>136007931</v>
       </c>
       <c r="B17" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>135840222</v>
       </c>
       <c r="B18" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>135840227</v>
       </c>
       <c r="B19" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>135840228</v>
       </c>
       <c r="B20" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135840233</v>
       </c>
       <c r="B2" t="n">
-        <v>79524</v>
+        <v>79528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135840235</v>
       </c>
       <c r="B3" t="n">
-        <v>79524</v>
+        <v>79528</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135840236</v>
       </c>
       <c r="B4" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135843493</v>
       </c>
       <c r="B5" t="n">
-        <v>92260</v>
+        <v>92266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135843492</v>
       </c>
       <c r="B6" t="n">
-        <v>92281</v>
+        <v>92287</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135840219</v>
       </c>
       <c r="B7" t="n">
-        <v>91989</v>
+        <v>91995</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135840223</v>
       </c>
       <c r="B8" t="n">
-        <v>91989</v>
+        <v>91995</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135843487</v>
       </c>
       <c r="B9" t="n">
-        <v>92733</v>
+        <v>92739</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135840232</v>
       </c>
       <c r="B10" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135840211</v>
       </c>
       <c r="B11" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135840213</v>
       </c>
       <c r="B12" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136007930</v>
       </c>
       <c r="B13" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135843491</v>
       </c>
       <c r="B14" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>135843489</v>
       </c>
       <c r="B15" t="n">
-        <v>58146</v>
+        <v>58150</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>135834021</v>
       </c>
       <c r="B16" t="n">
-        <v>58087</v>
+        <v>58091</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>136007931</v>
       </c>
       <c r="B17" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>135840222</v>
       </c>
       <c r="B18" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>135840227</v>
       </c>
       <c r="B19" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>135840228</v>
       </c>
       <c r="B20" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135840233</v>
       </c>
       <c r="B2" t="n">
-        <v>79528</v>
+        <v>79529</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135840235</v>
       </c>
       <c r="B3" t="n">
-        <v>79528</v>
+        <v>79529</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135840236</v>
       </c>
       <c r="B4" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135843493</v>
       </c>
       <c r="B5" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135843492</v>
       </c>
       <c r="B6" t="n">
-        <v>92287</v>
+        <v>92288</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135840219</v>
       </c>
       <c r="B7" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135840223</v>
       </c>
       <c r="B8" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135843487</v>
       </c>
       <c r="B9" t="n">
-        <v>92739</v>
+        <v>92740</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135840232</v>
       </c>
       <c r="B10" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135840211</v>
       </c>
       <c r="B11" t="n">
-        <v>80458</v>
+        <v>80459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135840213</v>
       </c>
       <c r="B12" t="n">
-        <v>80458</v>
+        <v>80459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136007930</v>
       </c>
       <c r="B13" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135843491</v>
       </c>
       <c r="B14" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>135843489</v>
       </c>
       <c r="B15" t="n">
-        <v>58150</v>
+        <v>58151</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>135834021</v>
       </c>
       <c r="B16" t="n">
-        <v>58091</v>
+        <v>58092</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>136007931</v>
       </c>
       <c r="B17" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>135840222</v>
       </c>
       <c r="B18" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>135840227</v>
       </c>
       <c r="B19" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>135840228</v>
       </c>
       <c r="B20" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135840233</v>
       </c>
       <c r="B2" t="n">
-        <v>79529</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135840235</v>
       </c>
       <c r="B3" t="n">
-        <v>79529</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135840236</v>
       </c>
       <c r="B4" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135843493</v>
       </c>
       <c r="B5" t="n">
-        <v>92267</v>
+        <v>92273</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135843492</v>
       </c>
       <c r="B6" t="n">
-        <v>92288</v>
+        <v>92294</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135840219</v>
       </c>
       <c r="B7" t="n">
-        <v>91996</v>
+        <v>92002</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135840223</v>
       </c>
       <c r="B8" t="n">
-        <v>91996</v>
+        <v>92002</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135843487</v>
       </c>
       <c r="B9" t="n">
-        <v>92740</v>
+        <v>92746</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135840232</v>
       </c>
       <c r="B10" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135840211</v>
       </c>
       <c r="B11" t="n">
-        <v>80459</v>
+        <v>80463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135840213</v>
       </c>
       <c r="B12" t="n">
-        <v>80459</v>
+        <v>80463</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136007930</v>
       </c>
       <c r="B13" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>136007931</v>
       </c>
       <c r="B17" t="n">
-        <v>98171</v>
+        <v>98182</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>135840222</v>
       </c>
       <c r="B18" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>135840227</v>
       </c>
       <c r="B19" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>135840228</v>
       </c>
       <c r="B20" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135840233</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135840235</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135840236</v>
       </c>
       <c r="B4" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135843493</v>
       </c>
       <c r="B5" t="n">
-        <v>92273</v>
+        <v>92280</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135843492</v>
       </c>
       <c r="B6" t="n">
-        <v>92294</v>
+        <v>92301</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135840219</v>
       </c>
       <c r="B7" t="n">
-        <v>92002</v>
+        <v>92009</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135840223</v>
       </c>
       <c r="B8" t="n">
-        <v>92002</v>
+        <v>92009</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135843487</v>
       </c>
       <c r="B9" t="n">
-        <v>92746</v>
+        <v>92753</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135840232</v>
       </c>
       <c r="B10" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135840211</v>
       </c>
       <c r="B11" t="n">
-        <v>80463</v>
+        <v>80469</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135840213</v>
       </c>
       <c r="B12" t="n">
-        <v>80463</v>
+        <v>80469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136007930</v>
       </c>
       <c r="B13" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135843491</v>
       </c>
       <c r="B14" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>135843489</v>
       </c>
       <c r="B15" t="n">
-        <v>58151</v>
+        <v>58156</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>135834021</v>
       </c>
       <c r="B16" t="n">
-        <v>58092</v>
+        <v>58097</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>136007931</v>
       </c>
       <c r="B17" t="n">
-        <v>98182</v>
+        <v>98195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>135840222</v>
       </c>
       <c r="B18" t="n">
-        <v>79477</v>
+        <v>79483</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>135840227</v>
       </c>
       <c r="B19" t="n">
-        <v>79477</v>
+        <v>79483</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>135840228</v>
       </c>
       <c r="B20" t="n">
-        <v>79477</v>
+        <v>79483</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>135843493</v>
       </c>
       <c r="B5" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
+          <t>Anna Öhlund, Christina Boyd, Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1131,7 +1131,7 @@
         <v>135843492</v>
       </c>
       <c r="B6" t="n">
-        <v>92301</v>
+        <v>92302</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
+          <t>Anna Öhlund, Christina Boyd, Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
         <v>135840219</v>
       </c>
       <c r="B7" t="n">
-        <v>92009</v>
+        <v>92010</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135840223</v>
       </c>
       <c r="B8" t="n">
-        <v>92009</v>
+        <v>92010</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135843487</v>
       </c>
       <c r="B9" t="n">
-        <v>92753</v>
+        <v>92754</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
+          <t>Anna Öhlund, Christina Boyd, Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
+          <t>Stefan Andersson, Christina Boyd, Anna Öhlund, per-erik mukka</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
+          <t>Anna Öhlund, Christina Boyd, Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2372,7 +2372,7 @@
         <v>136007931</v>
       </c>
       <c r="B17" t="n">
-        <v>98195</v>
+        <v>98196</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135840233</v>
       </c>
       <c r="B2" t="n">
-        <v>79539</v>
+        <v>79552</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135840235</v>
       </c>
       <c r="B3" t="n">
-        <v>79539</v>
+        <v>79552</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135840236</v>
       </c>
       <c r="B4" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135843493</v>
       </c>
       <c r="B5" t="n">
-        <v>92281</v>
+        <v>92294</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna Öhlund, Christina Boyd, Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1131,7 +1131,7 @@
         <v>135843492</v>
       </c>
       <c r="B6" t="n">
-        <v>92302</v>
+        <v>92315</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Öhlund, Christina Boyd, Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
         <v>135840219</v>
       </c>
       <c r="B7" t="n">
-        <v>92010</v>
+        <v>92023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135840223</v>
       </c>
       <c r="B8" t="n">
-        <v>92010</v>
+        <v>92023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135843487</v>
       </c>
       <c r="B9" t="n">
-        <v>92754</v>
+        <v>92767</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna Öhlund, Christina Boyd, Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1579,7 +1579,7 @@
         <v>135840232</v>
       </c>
       <c r="B10" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135840211</v>
       </c>
       <c r="B11" t="n">
-        <v>80469</v>
+        <v>80482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135840213</v>
       </c>
       <c r="B12" t="n">
-        <v>80469</v>
+        <v>80482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136007930</v>
       </c>
       <c r="B13" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135843491</v>
       </c>
       <c r="B14" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Christina Boyd, Anna Öhlund, per-erik mukka</t>
+          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2144,7 +2144,7 @@
         <v>135843489</v>
       </c>
       <c r="B15" t="n">
-        <v>58156</v>
+        <v>58169</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anna Öhlund, Christina Boyd, Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2256,7 +2256,7 @@
         <v>135834021</v>
       </c>
       <c r="B16" t="n">
-        <v>58097</v>
+        <v>58110</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>136007931</v>
       </c>
       <c r="B17" t="n">
-        <v>98196</v>
+        <v>98209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>135840222</v>
       </c>
       <c r="B18" t="n">
-        <v>79483</v>
+        <v>79496</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>135840227</v>
       </c>
       <c r="B19" t="n">
-        <v>79483</v>
+        <v>79496</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>135840228</v>
       </c>
       <c r="B20" t="n">
-        <v>79483</v>
+        <v>79496</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -1915,7 +1915,7 @@
         <v>136007930</v>
       </c>
       <c r="B13" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>136007931</v>
       </c>
       <c r="B17" t="n">
-        <v>98209</v>
+        <v>98210</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
